--- a/Excel/FestiveAttrConfig.xlsx
+++ b/Excel/FestiveAttrConfig.xlsx
@@ -322,12 +322,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1205,7 +1205,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>12</v>
@@ -1225,7 +1225,7 @@
         <v>18</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -1245,7 +1245,7 @@
         <v>19</v>
       </c>
       <c r="G8" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>14</v>
@@ -1265,7 +1265,7 @@
         <v>24</v>
       </c>
       <c r="G9" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -1285,7 +1285,7 @@
         <v>2003</v>
       </c>
       <c r="G10" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>16</v>
@@ -1305,7 +1305,7 @@
         <v>2001</v>
       </c>
       <c r="G11" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>17</v>
@@ -1325,7 +1325,7 @@
         <v>2002</v>
       </c>
       <c r="G12" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>18</v>
@@ -1348,7 +1348,7 @@
         <v>2007</v>
       </c>
       <c r="G13" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>19</v>
@@ -1370,7 +1370,7 @@
         <v>2008</v>
       </c>
       <c r="G14" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>20</v>
@@ -1395,7 +1395,7 @@
         <v>2009</v>
       </c>
       <c r="G15" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>21</v>
@@ -1418,7 +1418,7 @@
         <v>2012</v>
       </c>
       <c r="G16" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>22</v>
@@ -1438,7 +1438,7 @@
         <v>2010</v>
       </c>
       <c r="G17" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>23</v>
@@ -1458,7 +1458,7 @@
         <v>2013</v>
       </c>
       <c r="G18" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>24</v>
@@ -1478,7 +1478,7 @@
         <v>2004</v>
       </c>
       <c r="G19" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>19</v>
@@ -1500,7 +1500,7 @@
         <v>2005</v>
       </c>
       <c r="G20" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>20</v>
@@ -1525,7 +1525,7 @@
         <v>2006</v>
       </c>
       <c r="G21" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>25</v>
@@ -1548,7 +1548,7 @@
         <v>31</v>
       </c>
       <c r="G22" s="1">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>26</v>
@@ -1568,7 +1568,7 @@
         <v>32</v>
       </c>
       <c r="G23" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>27</v>

--- a/Excel/FestiveAttrConfig.xlsx
+++ b/Excel/FestiveAttrConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -144,6 +144,15 @@
   </si>
   <si>
     <t>命中</t>
+  </si>
+  <si>
+    <t>神话生命</t>
+  </si>
+  <si>
+    <t>神话防御</t>
+  </si>
+  <si>
+    <t>神话攻击</t>
   </si>
 </sst>
 </file>
@@ -322,12 +331,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1112,7 +1121,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1575,25 +1584,429 @@
       </c>
     </row>
     <row r="27" customFormat="1" ht="14" spans="1:18">
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="C27" s="1">
+        <v>101</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>20</v>
+      </c>
+      <c r="G27" s="1">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
     </row>
     <row r="28" customFormat="1" ht="14" spans="1:18">
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="81" customHeight="1"/>
+      <c r="C28" s="1">
+        <v>102</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1">
+        <v>18</v>
+      </c>
+      <c r="G28" s="1">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="C29" s="1">
+        <v>103</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>19</v>
+      </c>
+      <c r="G29" s="1">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="C30" s="1">
+        <v>104</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>24</v>
+      </c>
+      <c r="G30" s="1">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="C31" s="1">
+        <v>105</v>
+      </c>
+      <c r="D31" s="1">
+        <v>11</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1">
+        <v>2003</v>
+      </c>
+      <c r="G31" s="1">
+        <v>20</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="C32" s="1">
+        <v>106</v>
+      </c>
+      <c r="D32" s="1">
+        <v>11</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2001</v>
+      </c>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8">
+      <c r="C33" s="1">
+        <v>107</v>
+      </c>
+      <c r="D33" s="1">
+        <v>11</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G33" s="1">
+        <v>20</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8">
+      <c r="C34" s="1">
+        <v>108</v>
+      </c>
+      <c r="D34" s="1">
+        <v>21</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="F34" s="1">
+        <v>89</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8">
+      <c r="C35" s="1">
+        <v>109</v>
+      </c>
+      <c r="D35" s="1">
+        <v>21</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1">
+        <v>90</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8">
+      <c r="C36" s="1">
+        <v>110</v>
+      </c>
+      <c r="D36" s="1">
+        <v>21</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="1">
+        <v>91</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8">
+      <c r="C37" s="1">
+        <v>111</v>
+      </c>
+      <c r="D37" s="1">
+        <v>31</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2007</v>
+      </c>
+      <c r="G37" s="1">
+        <v>10</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8">
+      <c r="C38" s="1">
+        <v>112</v>
+      </c>
+      <c r="D38" s="1">
+        <v>31</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1">
+        <v>2008</v>
+      </c>
+      <c r="G38" s="1">
+        <v>10</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8">
+      <c r="C39" s="1">
+        <v>113</v>
+      </c>
+      <c r="D39" s="1">
+        <v>41</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2009</v>
+      </c>
+      <c r="G39" s="1">
+        <v>10</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8">
+      <c r="C40" s="1">
+        <v>114</v>
+      </c>
+      <c r="D40" s="1">
+        <v>41</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40" s="1">
+        <v>2012</v>
+      </c>
+      <c r="G40" s="1">
+        <v>20</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8">
+      <c r="C41" s="1">
+        <v>115</v>
+      </c>
+      <c r="D41" s="1">
+        <v>41</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1">
+        <v>2010</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8">
+      <c r="C42" s="1">
+        <v>116</v>
+      </c>
+      <c r="D42" s="1">
+        <v>51</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>2013</v>
+      </c>
+      <c r="G42" s="1">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8">
+      <c r="C43" s="1">
+        <v>117</v>
+      </c>
+      <c r="D43" s="1">
+        <v>51</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2004</v>
+      </c>
+      <c r="G43" s="1">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8">
+      <c r="C44" s="1">
+        <v>118</v>
+      </c>
+      <c r="D44" s="1">
+        <v>51</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1">
+        <v>2005</v>
+      </c>
+      <c r="G44" s="1">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8">
+      <c r="C45" s="1">
+        <v>119</v>
+      </c>
+      <c r="D45" s="1">
+        <v>51</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1">
+        <v>2006</v>
+      </c>
+      <c r="G45" s="1">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8">
+      <c r="C46" s="1">
+        <v>120</v>
+      </c>
+      <c r="D46" s="1">
+        <v>61</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="F46" s="1">
+        <v>31</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8">
+      <c r="C47" s="1">
+        <v>121</v>
+      </c>
+      <c r="D47" s="1">
+        <v>61</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1">
+        <v>32</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="81" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:H5 C3:F5" errorStyle="warning">

--- a/Excel/FestiveAttrConfig.xlsx
+++ b/Excel/FestiveAttrConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -1737,7 +1742,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -1757,7 +1762,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
